--- a/Work_Summary.xlsx
+++ b/Work_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ganesh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58ACE17B-CF55-4C8A-8653-78B00D9EAA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4D320E-855A-4C3F-B2AC-5019EEF98F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{778CDF9F-1D4A-45BA-9983-59D1E0596ECD}"/>
   </bookViews>
@@ -183,9 +183,6 @@
 7.Modified an existing Wireshark script so it collects "any" network files during the night endurance and keeps the last ten.</t>
   </si>
   <si>
-    <t xml:space="preserve">Micallaneous </t>
-  </si>
-  <si>
     <t>1. Wrote common Flash Procedure (which includes instructions how to flash and what precautions to take when flashing with images as reference)
 2. Wrote Mini Python log parsing scripts and scripts for file read/write operations 
 3. Peer reviews of STP documents for DEJ_WB8G and SNS100.</t>
@@ -194,6 +191,9 @@
     <t>1.New joiners follow the document and flash the hardware on their own, without needing someone to guide them.
 2. Saves manual effort on repetitive log and file work. Used in CADF2 and other filtering tasks.
 3. The reviews caught many mistakes in the documents before they were finalised for QA audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miscellaneous </t>
   </si>
 </sst>
 </file>
@@ -324,11 +324,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -653,10 +653,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="11"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -807,13 +807,13 @@
     </row>
     <row r="17" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="C17" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
